--- a/artfynd/S 1543-2026 artfynd.xlsx
+++ b/artfynd/S 1543-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AZ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96014180</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125796881</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96076521</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1153,6 +1173,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101706401</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1268,6 +1293,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133339906</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1393,6 +1423,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109593219</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1518,6 +1553,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125917036</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1643,6 +1683,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111297162</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1773,6 +1818,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102526634</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1898,6 +1948,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94816563</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2023,6 +2078,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94816578</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2148,6 +2208,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102136850</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2273,6 +2338,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95160317</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2397,6 +2467,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92895445</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2516,6 +2591,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101847269</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2639,6 +2719,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94733638</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2762,6 +2847,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125917020</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2881,6 +2971,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94991424</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3000,6 +3095,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94509990</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3119,6 +3219,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96014172</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3238,6 +3343,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125932789</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3361,6 +3471,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96079230</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3480,6 +3595,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125917040</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3601,6 +3721,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134922879</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3726,6 +3851,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134922947</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3847,6 +3977,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94769831</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3972,6 +4107,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134922840</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4097,6 +4237,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94369274</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4218,6 +4363,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134922920</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4343,6 +4493,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126633201</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4468,6 +4623,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110405840</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4593,6 +4753,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134922935</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4722,6 +4887,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94389041</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4858,6 +5028,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15149237</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4983,6 +5158,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127125312</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5108,6 +5288,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127130314</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5227,6 +5412,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111011264</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5344,6 +5534,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111402443</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5465,6 +5660,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96362333</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5590,6 +5790,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101580451</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5705,6 +5910,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110154574</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5830,6 +6040,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125796681</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5954,6 +6169,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134923214</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6070,6 +6290,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101475765</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6180,6 +6405,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101630080</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6290,6 +6520,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101630089</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6415,6 +6650,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133824031</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6517,6 +6757,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232596</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6637,6 +6882,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94335840</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6747,8 +6997,65 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101630096</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 1543-2026 artfynd.xlsx
+++ b/artfynd/S 1543-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ51"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6890,10 +6890,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>101630096</v>
+        <v>135590389</v>
       </c>
       <c r="B51" t="n">
-        <v>102560</v>
+        <v>13464</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6901,46 +6901,46 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222133</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Jungfrulin</t>
-        </is>
+        <v>236246</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Myopa fasciata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Meigen, 1804</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tränkärret, O, Nrk</t>
+          <t>Vita mossen, Nrk</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507117</v>
+        <v>507074</v>
       </c>
       <c r="R51" t="n">
-        <v>6535565</v>
+        <v>6535257</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -6967,12 +6967,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6988,16 +6998,131 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135590389</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>101630096</v>
+      </c>
+      <c r="B52" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Tränkärret, O, Nrk</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>507117</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6535565</v>
+      </c>
+      <c r="S52" t="n">
+        <v>50</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/101630096</t>
         </is>
@@ -7055,6 +7180,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1543-2026 artfynd.xlsx
+++ b/artfynd/S 1543-2026 artfynd.xlsx
@@ -3606,7 +3606,7 @@
         <v>134922879</v>
       </c>
       <c r="B25" t="n">
-        <v>61527</v>
+        <v>61536</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>134922947</v>
       </c>
       <c r="B26" t="n">
-        <v>61527</v>
+        <v>61536</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>134922840</v>
       </c>
       <c r="B28" t="n">
-        <v>43224</v>
+        <v>43229</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>134922920</v>
       </c>
       <c r="B30" t="n">
-        <v>43383</v>
+        <v>43388</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         <v>134922935</v>
       </c>
       <c r="B33" t="n">
-        <v>43290</v>
+        <v>43295</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>134923214</v>
       </c>
       <c r="B44" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         <v>135590389</v>
       </c>
       <c r="B51" t="n">
-        <v>13464</v>
+        <v>13466</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/S 1543-2026 artfynd.xlsx
+++ b/artfynd/S 1543-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ51"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6890,10 +6890,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>101630096</v>
+        <v>135590389</v>
       </c>
       <c r="B51" t="n">
-        <v>102560</v>
+        <v>13466</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6901,46 +6901,46 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222133</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Jungfrulin</t>
-        </is>
+        <v>236246</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Myopa fasciata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Meigen, 1804</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tränkärret, O, Nrk</t>
+          <t>Vita mossen, Nrk</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507117</v>
+        <v>507074</v>
       </c>
       <c r="R51" t="n">
-        <v>6535565</v>
+        <v>6535257</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -6967,12 +6967,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6988,16 +6998,131 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135590389</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>101630096</v>
+      </c>
+      <c r="B52" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Tränkärret, O, Nrk</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>507117</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6535565</v>
+      </c>
+      <c r="S52" t="n">
+        <v>50</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/101630096</t>
         </is>
@@ -7055,6 +7180,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1543-2026 artfynd.xlsx
+++ b/artfynd/S 1543-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ52"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1181,40 +1181,44 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133339906</v>
+        <v>135980855</v>
       </c>
       <c r="B6" t="n">
-        <v>57162</v>
+        <v>57865</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1254,22 +1258,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1295,38 +1299,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133339906</t>
+          <t>https://artportalen.se/Sighting/135980855</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109593219</v>
+        <v>135981312</v>
       </c>
       <c r="B7" t="n">
-        <v>43283</v>
+        <v>57865</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100770</v>
+        <v>100100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre blåvinge</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cupido minimus</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fuessly, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1334,29 +1338,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vita Mossen, S Nyckelhult, Nrk</t>
+          <t>Vita mossen, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507118</v>
+        <v>507074</v>
       </c>
       <c r="R7" t="n">
-        <v>6535342</v>
+        <v>6535257</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1383,22 +1382,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,86 +1406,76 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109593219</t>
+          <t>https://artportalen.se/Sighting/135981312</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125917036</v>
+        <v>133339906</v>
       </c>
       <c r="B8" t="n">
-        <v>43283</v>
+        <v>57162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100770</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre blåvinge</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cupido minimus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fuessly, 1775)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vita mossen, Nrk</t>
+          <t>Vita Mossen, S Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507074</v>
+        <v>507118</v>
       </c>
       <c r="R8" t="n">
-        <v>6535257</v>
+        <v>6535342</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1513,22 +1502,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1537,56 +1526,55 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125917036</t>
+          <t>https://artportalen.se/Sighting/133339906</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111297162</v>
+        <v>109593219</v>
       </c>
       <c r="B9" t="n">
-        <v>43212</v>
+        <v>43283</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101070</v>
+        <v>100770</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Silversmygare</t>
+          <t>Mindre blåvinge</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hesperia comma</t>
+          <t>Cupido minimus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fuessly, 1775)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1643,22 +1631,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1685,16 +1673,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111297162</t>
+          <t>https://artportalen.se/Sighting/109593219</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102526634</v>
+        <v>125917036</v>
       </c>
       <c r="B10" t="n">
-        <v>29490</v>
+        <v>43283</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1702,21 +1690,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101401</v>
+        <v>100770</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Silvergökbi</t>
+          <t>Mindre blåvinge</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nomada argentata</t>
+          <t>Cupido minimus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Herrich-Schäffer, 1839</t>
+          <t>(Fuessly, 1775)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1733,20 +1721,20 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vita Mossen, S Nyckelhult, Nrk</t>
+          <t>Vita mossen, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507118</v>
+        <v>507074</v>
       </c>
       <c r="R10" t="n">
-        <v>6535342</v>
+        <v>6535257</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1773,27 +1761,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Upptäcktes av Helena Johansson.</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1809,49 +1792,49 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102526634</t>
+          <t>https://artportalen.se/Sighting/125917036</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>94816563</v>
+        <v>111297162</v>
       </c>
       <c r="B11" t="n">
-        <v>45049</v>
+        <v>43212</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102021</v>
+        <v>101070</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Silversmygare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Hesperia comma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1868,7 +1851,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1908,22 +1891,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1950,38 +1933,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94816563</t>
+          <t>https://artportalen.se/Sighting/111297162</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>94816578</v>
+        <v>102526634</v>
       </c>
       <c r="B12" t="n">
-        <v>45033</v>
+        <v>29490</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102366</v>
+        <v>101401</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ängsmetallvinge</t>
+          <t>Silvergökbi</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Adscita statices</t>
+          <t>Nomada argentata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Herrich-Schäffer, 1839</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2038,22 +2021,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Upptäcktes av Helena Johansson.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2080,38 +2068,38 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94816578</t>
+          <t>https://artportalen.se/Sighting/102526634</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>102136850</v>
+        <v>94816563</v>
       </c>
       <c r="B13" t="n">
-        <v>40128</v>
+        <v>45049</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102471</v>
+        <v>102021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Åkerväddsantennmal</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nemophora metallica</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Poda, 1761)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2128,7 +2116,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2168,22 +2156,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-07-08</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-07-08</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2210,16 +2198,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102136850</t>
+          <t>https://artportalen.se/Sighting/94816563</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>95160317</v>
+        <v>94816578</v>
       </c>
       <c r="B14" t="n">
-        <v>18920</v>
+        <v>45033</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,21 +2215,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102557</v>
+        <v>102366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk bronsblomfluga</t>
+          <t>Ängsmetallvinge</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callicera aurata</t>
+          <t>Adscita statices</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Rossi, 1790)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2298,22 +2286,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-07-29</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-07-29</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2340,66 +2328,71 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95160317</t>
+          <t>https://artportalen.se/Sighting/94816578</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>92895445</v>
+        <v>102136850</v>
       </c>
       <c r="B15" t="n">
-        <v>57144</v>
+        <v>40128</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102613</v>
+        <v>102471</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Åkerväddsantennmal</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Nemophora metallica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Poda, 1761)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tränkärret, Nrk</t>
+          <t>Vita Mossen, S Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507028</v>
+        <v>507118</v>
       </c>
       <c r="R15" t="n">
-        <v>6535261</v>
+        <v>6535342</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2423,27 +2416,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-04-30</t>
+          <t>2022-07-08</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-04-30</t>
+          <t>2022-07-08</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Stöttes.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2452,6 +2440,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2469,38 +2458,38 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92895445</t>
+          <t>https://artportalen.se/Sighting/102136850</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>101847269</v>
+        <v>95160317</v>
       </c>
       <c r="B16" t="n">
-        <v>58129</v>
+        <v>18920</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102623</v>
+        <v>102557</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Mörk bronsblomfluga</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Callicera aurata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rossi, 1790)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2508,11 +2497,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2552,7 +2546,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-06-24</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2562,12 +2556,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-06-24</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2576,6 +2570,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2593,16 +2588,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101847269</t>
+          <t>https://artportalen.se/Sighting/95160317</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>94733638</v>
+        <v>92895445</v>
       </c>
       <c r="B17" t="n">
-        <v>58039</v>
+        <v>57144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2610,53 +2605,49 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102626</v>
+        <v>102613</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vita Mossen, S Nyckelhult, Nrk</t>
+          <t>Tränkärret, Nrk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507118</v>
+        <v>507028</v>
       </c>
       <c r="R17" t="n">
-        <v>6535342</v>
+        <v>6535261</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2680,22 +2671,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2021-04-30</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2021-04-30</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Stöttes.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2721,16 +2717,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94733638</t>
+          <t>https://artportalen.se/Sighting/92895445</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125917020</v>
+        <v>101847269</v>
       </c>
       <c r="B18" t="n">
-        <v>58039</v>
+        <v>58129</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2738,21 +2734,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102626</v>
+        <v>102623</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2761,27 +2757,23 @@
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vita mossen, Nrk</t>
+          <t>Vita Mossen, S Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507074</v>
+        <v>507118</v>
       </c>
       <c r="R18" t="n">
-        <v>6535257</v>
+        <v>6535342</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2808,22 +2800,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2022-06-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-06-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>09:30</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2838,61 +2830,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125917020</t>
+          <t>https://artportalen.se/Sighting/101847269</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>94991424</v>
+        <v>94733638</v>
       </c>
       <c r="B19" t="n">
-        <v>57774</v>
+        <v>58039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102976</v>
+        <v>102626</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2932,22 +2928,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-07-20</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-07-20</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2973,33 +2969,33 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94991424</t>
+          <t>https://artportalen.se/Sighting/94733638</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>94509990</v>
+        <v>125917020</v>
       </c>
       <c r="B20" t="n">
-        <v>58541</v>
+        <v>58039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102987</v>
+        <v>102626</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3013,23 +3009,27 @@
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vita Mossen, S Nyckelhult, Nrk</t>
+          <t>Vita mossen, Nrk</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507118</v>
+        <v>507074</v>
       </c>
       <c r="R20" t="n">
-        <v>6535342</v>
+        <v>6535257</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -3056,22 +3056,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-06-27</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-06-27</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3086,44 +3086,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94509990</t>
+          <t>https://artportalen.se/Sighting/125917020</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96014172</v>
+        <v>94991424</v>
       </c>
       <c r="B21" t="n">
-        <v>58463</v>
+        <v>57774</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102995</v>
+        <v>102976</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3133,14 +3133,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3221,16 +3221,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96014172</t>
+          <t>https://artportalen.se/Sighting/94991424</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125932789</v>
+        <v>94509990</v>
       </c>
       <c r="B22" t="n">
-        <v>58238</v>
+        <v>58541</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103012</v>
+        <v>102987</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3264,23 +3264,23 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tränkärret, Nrk</t>
+          <t>Vita Mossen, S Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507028</v>
+        <v>507118</v>
       </c>
       <c r="R22" t="n">
-        <v>6535261</v>
+        <v>6535342</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3304,22 +3304,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2021-06-27</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2021-06-27</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3334,49 +3334,49 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Frank Tholfsson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Frank Tholfsson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125932789</t>
+          <t>https://artportalen.se/Sighting/94509990</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>96079230</v>
+        <v>96014172</v>
       </c>
       <c r="B23" t="n">
-        <v>58676</v>
+        <v>58463</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103055</v>
+        <v>102995</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3385,11 +3385,7 @@
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>rastande</t>
@@ -3432,22 +3428,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3473,16 +3469,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96079230</t>
+          <t>https://artportalen.se/Sighting/96014172</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125917040</v>
+        <v>125932789</v>
       </c>
       <c r="B24" t="n">
-        <v>58676</v>
+        <v>58238</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3490,21 +3486,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103055</v>
+        <v>103012</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3522,17 +3518,17 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vita mossen, Nrk</t>
+          <t>Tränkärret, Nrk</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507074</v>
+        <v>507028</v>
       </c>
       <c r="R24" t="n">
-        <v>6535257</v>
+        <v>6535261</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3556,22 +3552,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3586,27 +3582,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Frank Tholfsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Frank Tholfsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125917040</t>
+          <t>https://artportalen.se/Sighting/125932789</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134922879</v>
+        <v>96079230</v>
       </c>
       <c r="B25" t="n">
-        <v>61536</v>
+        <v>58676</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3614,21 +3610,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106670</v>
+        <v>103055</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Arion ater ater</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3636,12 +3632,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>frispringande/krypande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3681,22 +3680,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3705,7 +3704,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3723,16 +3721,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134922879</t>
+          <t>https://artportalen.se/Sighting/96079230</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134922947</v>
+        <v>125917040</v>
       </c>
       <c r="B26" t="n">
-        <v>61536</v>
+        <v>58676</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3740,21 +3738,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106670</v>
+        <v>103055</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Arion ater ater</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3762,16 +3760,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>frispringande/krypande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3811,7 +3804,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -3821,21 +3814,20 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF26" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3853,16 +3845,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134922947</t>
+          <t>https://artportalen.se/Sighting/125917040</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>94769831</v>
+        <v>134922879</v>
       </c>
       <c r="B27" t="n">
-        <v>43219</v>
+        <v>61536</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3870,34 +3862,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>201028</v>
+        <v>106670</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Thymelicus lineola</t>
+          <t>Arion ater ater</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ochsenheimer, 1808)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>frispringande/krypande</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3937,17 +3929,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -3979,16 +3971,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94769831</t>
+          <t>https://artportalen.se/Sighting/134922879</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134922840</v>
+        <v>134922947</v>
       </c>
       <c r="B28" t="n">
-        <v>43229</v>
+        <v>61536</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3996,21 +3988,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>201028</v>
+        <v>106670</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thymelicus lineola</t>
+          <t>Arion ater ater</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ochsenheimer, 1808)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4027,7 +4019,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>frispringande/krypande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4089,7 +4081,7 @@
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
@@ -4109,45 +4101,41 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134922840</t>
+          <t>https://artportalen.se/Sighting/134922947</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>94369274</v>
+        <v>94769831</v>
       </c>
       <c r="B29" t="n">
-        <v>43378</v>
+        <v>43219</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>201075</v>
+        <v>201028</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Boloria selene</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ochsenheimer, 1808)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
@@ -4157,7 +4145,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4197,7 +4185,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -4207,12 +4195,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4239,41 +4227,45 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94369274</t>
+          <t>https://artportalen.se/Sighting/94769831</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134922920</v>
+        <v>134922840</v>
       </c>
       <c r="B30" t="n">
-        <v>43388</v>
+        <v>43229</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>201075</v>
+        <v>201028</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Boloria selene</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Ochsenheimer, 1808)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
@@ -4365,16 +4357,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134922920</t>
+          <t>https://artportalen.se/Sighting/134922840</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126633201</v>
+        <v>94369274</v>
       </c>
       <c r="B31" t="n">
-        <v>43454</v>
+        <v>43378</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4382,21 +4374,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>201108</v>
+        <v>201075</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Starrgräsfjäril</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Coenonympha tullia</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Müller, 1764)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4453,22 +4445,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4495,45 +4487,41 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126633201</t>
+          <t>https://artportalen.se/Sighting/94369274</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>110405840</v>
+        <v>134922920</v>
       </c>
       <c r="B32" t="n">
-        <v>43258</v>
+        <v>43388</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>201129</v>
+        <v>201075</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycaena virgaureae</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
@@ -4549,14 +4537,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vita Mossen, S Nyckelhult, Nrk</t>
+          <t>Vita mossen, Nrk</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507118</v>
+        <v>507074</v>
       </c>
       <c r="R32" t="n">
-        <v>6535342</v>
+        <v>6535257</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4583,22 +4571,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4614,27 +4602,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110405840</t>
+          <t>https://artportalen.se/Sighting/134922920</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134922935</v>
+        <v>126633201</v>
       </c>
       <c r="B33" t="n">
-        <v>43295</v>
+        <v>43454</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4642,21 +4630,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>201143</v>
+        <v>201108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ängsblåvinge</t>
+          <t>Starrgräsfjäril</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cyaniris semiargus</t>
+          <t>Coenonympha tullia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Rottemburg, 1775)</t>
+          <t>(Müller, 1764)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4679,14 +4667,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vita mossen, Nrk</t>
+          <t>Vita Mossen, S Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507074</v>
+        <v>507118</v>
       </c>
       <c r="R33" t="n">
-        <v>6535257</v>
+        <v>6535342</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4713,17 +4701,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4744,49 +4732,49 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134922935</t>
+          <t>https://artportalen.se/Sighting/126633201</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>94389041</v>
+        <v>110405840</v>
       </c>
       <c r="B34" t="n">
-        <v>43309</v>
+        <v>43258</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>201146</v>
+        <v>201129</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Polyommatus amandus</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schneider, 1792)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4800,14 +4788,10 @@
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4847,17 +4831,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -4889,16 +4873,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94389041</t>
+          <t>https://artportalen.se/Sighting/110405840</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>15149237</v>
+        <v>134922935</v>
       </c>
       <c r="B35" t="n">
-        <v>45042</v>
+        <v>43295</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4906,21 +4890,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>201164</v>
+        <v>201143</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sexfläckig bastardsvärmare</t>
+          <t>Ängsblåvinge</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Zygaena filipendulae</t>
+          <t>Cyaniris semiargus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4928,31 +4912,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Axsjöfallet 7450/0750, Nrk</t>
+          <t>Vita mossen, Nrk</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>507082</v>
+        <v>507074</v>
       </c>
       <c r="R35" t="n">
-        <v>6535272</v>
+        <v>6535257</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4979,27 +4961,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2012-07-31</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2012-07-31</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På Succisa</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5008,38 +4985,34 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Ängsmark</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/15149237</t>
+          <t>https://artportalen.se/Sighting/134922935</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127125312</v>
+        <v>94389041</v>
       </c>
       <c r="B36" t="n">
-        <v>45042</v>
+        <v>43309</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5047,21 +5020,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>201164</v>
+        <v>201146</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sexfläckig bastardsvärmare</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Zygaena filipendulae</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schneider, 1792)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -5075,10 +5048,14 @@
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5118,22 +5095,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5160,13 +5137,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127125312</t>
+          <t>https://artportalen.se/Sighting/94389041</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127130314</v>
+        <v>15149237</v>
       </c>
       <c r="B37" t="n">
         <v>45042</v>
@@ -5199,29 +5176,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vita mossen, Nrk</t>
+          <t>Axsjöfallet 7450/0750, Nrk</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507074</v>
+        <v>507082</v>
       </c>
       <c r="R37" t="n">
-        <v>6535257</v>
+        <v>6535272</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -5248,22 +5227,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2012-07-31</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2012-07-31</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På Succisa</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5272,51 +5256,55 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Ängsmark</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Gunnar Hallin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Gunnar Hallin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127130314</t>
+          <t>https://artportalen.se/Sighting/15149237</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>111011264</v>
+        <v>127125312</v>
       </c>
       <c r="B38" t="n">
-        <v>56689</v>
+        <v>45042</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>206046</v>
+        <v>201164</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Zygaena filipendulae</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5329,11 +5317,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>gående/springande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5373,22 +5366,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-07-23</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-07-23</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5397,6 +5390,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5414,33 +5408,33 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111011264</t>
+          <t>https://artportalen.se/Sighting/127125312</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>111402443</v>
+        <v>127130314</v>
       </c>
       <c r="B39" t="n">
-        <v>58790</v>
+        <v>45042</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>208245</v>
+        <v>201164</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Zygaena filipendulae</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5454,20 +5448,28 @@
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vita Mossen, S Nyckelhult, Nrk</t>
+          <t>Vita mossen, Nrk</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507118</v>
+        <v>507074</v>
       </c>
       <c r="R39" t="n">
-        <v>6535342</v>
+        <v>6535257</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -5494,17 +5496,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5525,49 +5527,49 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111402443</t>
+          <t>https://artportalen.se/Sighting/127130314</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>96362333</v>
+        <v>111011264</v>
       </c>
       <c r="B40" t="n">
-        <v>58817</v>
+        <v>56689</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>208249</v>
+        <v>206046</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5575,12 +5577,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>gående/springande</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5620,22 +5621,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2023-07-23</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2023-07-23</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5644,7 +5645,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5662,38 +5662,38 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96362333</t>
+          <t>https://artportalen.se/Sighting/111011264</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>101580451</v>
+        <v>111402443</v>
       </c>
       <c r="B41" t="n">
-        <v>42274</v>
+        <v>58790</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>215930</v>
+        <v>208245</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jungfrulinsfly</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phytometra viridaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Clerck, 1759)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5702,17 +5702,9 @@
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5750,7 +5742,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
@@ -5760,12 +5752,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5792,38 +5784,38 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101580451</t>
+          <t>https://artportalen.se/Sighting/111402443</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>110154574</v>
+        <v>96362333</v>
       </c>
       <c r="B42" t="n">
-        <v>42274</v>
+        <v>58817</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>215930</v>
+        <v>208249</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Jungfrulinsfly</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phytometra viridaria</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Clerck, 1759)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5832,28 +5824,24 @@
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tränkärret, SO, Nrk</t>
+          <t>Vita Mossen, S Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507125</v>
+        <v>507118</v>
       </c>
       <c r="R42" t="n">
-        <v>6535353</v>
+        <v>6535342</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5880,12 +5868,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5901,24 +5899,24 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110154574</t>
+          <t>https://artportalen.se/Sighting/96362333</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125796681</v>
+        <v>101580451</v>
       </c>
       <c r="B43" t="n">
         <v>42274</v>
@@ -5960,20 +5958,20 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vita mossen, Nrk</t>
+          <t>Vita Mossen, S Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507074</v>
+        <v>507118</v>
       </c>
       <c r="R43" t="n">
-        <v>6535257</v>
+        <v>6535342</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -6000,22 +5998,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6031,49 +6029,49 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125796681</t>
+          <t>https://artportalen.se/Sighting/101580451</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134923214</v>
+        <v>110154574</v>
       </c>
       <c r="B44" t="n">
-        <v>99159</v>
+        <v>42274</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219790</v>
+        <v>215930</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Jungfrulinsfly</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phytometra viridaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Clerck, 1759)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -6081,28 +6079,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vita mossen, Nrk</t>
+          <t>Tränkärret, SO, Nrk</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507074</v>
+        <v>507125</v>
       </c>
       <c r="R44" t="n">
-        <v>6535257</v>
+        <v>6535353</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -6129,22 +6128,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6160,27 +6149,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134923214</t>
+          <t>https://artportalen.se/Sighting/110154574</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>101475765</v>
+        <v>125796681</v>
       </c>
       <c r="B45" t="n">
-        <v>102560</v>
+        <v>42274</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6188,42 +6177,51 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222133</v>
+        <v>215930</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Jungfrulinsfly</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Phytometra viridaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Clerck, 1759)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vita Mossen, S Nyckelhult, Nrk</t>
+          <t>Vita mossen, Nrk</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507118</v>
+        <v>507074</v>
       </c>
       <c r="R45" t="n">
-        <v>6535342</v>
+        <v>6535257</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -6250,22 +6248,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6281,52 +6279,56 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101475765</t>
+          <t>https://artportalen.se/Sighting/125796681</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>101630080</v>
+        <v>134923214</v>
       </c>
       <c r="B46" t="n">
-        <v>102560</v>
+        <v>99159</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222133</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -6341,14 +6343,14 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tränkärret, NO om, Nrk</t>
+          <t>Vita mossen, Nrk</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>507115</v>
+        <v>507074</v>
       </c>
       <c r="R46" t="n">
-        <v>6535448</v>
+        <v>6535257</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -6375,12 +6377,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6396,24 +6408,24 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101630080</t>
+          <t>https://artportalen.se/Sighting/134923214</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>101630089</v>
+        <v>101475765</v>
       </c>
       <c r="B47" t="n">
         <v>102560</v>
@@ -6442,11 +6454,7 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -6456,14 +6464,14 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tränkärret, SO, Nrk</t>
+          <t>Vita Mossen, S Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507125</v>
+        <v>507118</v>
       </c>
       <c r="R47" t="n">
-        <v>6535353</v>
+        <v>6535342</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -6490,12 +6498,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6511,27 +6529,27 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101630089</t>
+          <t>https://artportalen.se/Sighting/101475765</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133824031</v>
+        <v>101630080</v>
       </c>
       <c r="B48" t="n">
-        <v>102637</v>
+        <v>102560</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6556,12 +6574,12 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -6571,14 +6589,14 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Vita mossen, Nrk</t>
+          <t>Tränkärret, NO om, Nrk</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507074</v>
+        <v>507115</v>
       </c>
       <c r="R48" t="n">
-        <v>6535257</v>
+        <v>6535448</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -6605,27 +6623,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6641,27 +6644,27 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133824031</t>
+          <t>https://artportalen.se/Sighting/101630080</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134232596</v>
+        <v>101630089</v>
       </c>
       <c r="B49" t="n">
-        <v>102637</v>
+        <v>102560</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6687,19 +6690,31 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lerbäck, Nrk</t>
+          <t>Tränkärret, SO, Nrk</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507058</v>
+        <v>507125</v>
       </c>
       <c r="R49" t="n">
-        <v>6535246</v>
+        <v>6535353</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6723,17 +6738,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6742,33 +6752,34 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134232596</t>
+          <t>https://artportalen.se/Sighting/101630089</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>94335840</v>
+        <v>133824031</v>
       </c>
       <c r="B50" t="n">
-        <v>13460</v>
+        <v>102637</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6776,16 +6787,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>236246</v>
+        <v>222133</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Myopa fasciata</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Meigen, 1804</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -6796,26 +6812,21 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vita Mossen, S Nyckelhult, Nrk</t>
+          <t>Vita mossen, Nrk</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507118</v>
+        <v>507074</v>
       </c>
       <c r="R50" t="n">
-        <v>6535342</v>
+        <v>6535257</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -6842,22 +6853,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6873,27 +6889,27 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94335840</t>
+          <t>https://artportalen.se/Sighting/133824031</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135590389</v>
+        <v>134232596</v>
       </c>
       <c r="B51" t="n">
-        <v>13466</v>
+        <v>102637</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6901,49 +6917,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>236246</v>
+        <v>222133</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Myopa fasciata</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Meigen, 1804</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vita mossen, Nrk</t>
+          <t>Lerbäck, Nrk</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507074</v>
+        <v>507058</v>
       </c>
       <c r="R51" t="n">
-        <v>6535257</v>
+        <v>6535246</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6967,22 +6971,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6991,34 +6990,33 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135590389</t>
+          <t>https://artportalen.se/Sighting/134232596</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>101630096</v>
+        <v>94335840</v>
       </c>
       <c r="B52" t="n">
-        <v>102560</v>
+        <v>13460</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7026,46 +7024,46 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222133</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Jungfrulin</t>
-        </is>
+        <v>236246</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Myopa fasciata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Meigen, 1804</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Tränkärret, O, Nrk</t>
+          <t>Vita Mossen, S Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507117</v>
+        <v>507118</v>
       </c>
       <c r="R52" t="n">
-        <v>6535565</v>
+        <v>6535342</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -7092,12 +7090,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7113,16 +7121,256 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94335840</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135590389</v>
+      </c>
+      <c r="B53" t="n">
+        <v>13466</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>236246</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Myopa fasciata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Meigen, 1804</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Vita mossen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>507074</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6535257</v>
+      </c>
+      <c r="S53" t="n">
+        <v>50</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135590389</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>101630096</v>
+      </c>
+      <c r="B54" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Tränkärret, O, Nrk</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>507117</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6535565</v>
+      </c>
+      <c r="S54" t="n">
+        <v>50</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/101630096</t>
         </is>
@@ -7181,6 +7429,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1543-2026 artfynd.xlsx
+++ b/artfynd/S 1543-2026 artfynd.xlsx
@@ -1184,7 +1184,7 @@
         <v>135980855</v>
       </c>
       <c r="B6" t="n">
-        <v>57865</v>
+        <v>57867</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>135981312</v>
       </c>
       <c r="B7" t="n">
-        <v>57865</v>
+        <v>57867</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>135590389</v>
       </c>
       <c r="B53" t="n">
-        <v>13466</v>
+        <v>13468</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/S 1543-2026 artfynd.xlsx
+++ b/artfynd/S 1543-2026 artfynd.xlsx
@@ -1184,7 +1184,7 @@
         <v>135980855</v>
       </c>
       <c r="B6" t="n">
-        <v>57867</v>
+        <v>57868</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>135981312</v>
       </c>
       <c r="B7" t="n">
-        <v>57867</v>
+        <v>57868</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 1543-2026 artfynd.xlsx
+++ b/artfynd/S 1543-2026 artfynd.xlsx
@@ -1184,7 +1184,7 @@
         <v>135980855</v>
       </c>
       <c r="B6" t="n">
-        <v>57868</v>
+        <v>57872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>135981312</v>
       </c>
       <c r="B7" t="n">
-        <v>57868</v>
+        <v>57872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 1543-2026 artfynd.xlsx
+++ b/artfynd/S 1543-2026 artfynd.xlsx
@@ -1184,7 +1184,7 @@
         <v>135980855</v>
       </c>
       <c r="B6" t="n">
-        <v>57872</v>
+        <v>57873</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>135981312</v>
       </c>
       <c r="B7" t="n">
-        <v>57872</v>
+        <v>57873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 1543-2026 artfynd.xlsx
+++ b/artfynd/S 1543-2026 artfynd.xlsx
@@ -1184,7 +1184,7 @@
         <v>135980855</v>
       </c>
       <c r="B6" t="n">
-        <v>57873</v>
+        <v>57878</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>135981312</v>
       </c>
       <c r="B7" t="n">
-        <v>57873</v>
+        <v>57878</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 1543-2026 artfynd.xlsx
+++ b/artfynd/S 1543-2026 artfynd.xlsx
@@ -1184,7 +1184,7 @@
         <v>135980855</v>
       </c>
       <c r="B6" t="n">
-        <v>57878</v>
+        <v>57891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>135981312</v>
       </c>
       <c r="B7" t="n">
-        <v>57878</v>
+        <v>57891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
